--- a/DataframeClusters.xlsx
+++ b/DataframeClusters.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuri\Desktop\Overleaf - Métodos Quantitativos II\Aula 1 - Parte 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yuri\Desktop\Overleaf - Métodos Quantitativos II\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -29,90 +29,6 @@
     <t>Empresa</t>
   </si>
   <si>
-    <t>E01</t>
-  </si>
-  <si>
-    <t>E02</t>
-  </si>
-  <si>
-    <t>E03</t>
-  </si>
-  <si>
-    <t>E04</t>
-  </si>
-  <si>
-    <t>E05</t>
-  </si>
-  <si>
-    <t>E06</t>
-  </si>
-  <si>
-    <t>E07</t>
-  </si>
-  <si>
-    <t>E08</t>
-  </si>
-  <si>
-    <t>E09</t>
-  </si>
-  <si>
-    <t>E10</t>
-  </si>
-  <si>
-    <t>E11</t>
-  </si>
-  <si>
-    <t>E12</t>
-  </si>
-  <si>
-    <t>E13</t>
-  </si>
-  <si>
-    <t>E14</t>
-  </si>
-  <si>
-    <t>E15</t>
-  </si>
-  <si>
-    <t>E16</t>
-  </si>
-  <si>
-    <t>E17</t>
-  </si>
-  <si>
-    <t>E18</t>
-  </si>
-  <si>
-    <t>E19</t>
-  </si>
-  <si>
-    <t>E20</t>
-  </si>
-  <si>
-    <t>E21</t>
-  </si>
-  <si>
-    <t>E22</t>
-  </si>
-  <si>
-    <t>E23</t>
-  </si>
-  <si>
-    <t>E24</t>
-  </si>
-  <si>
-    <t>E25</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>E27</t>
-  </si>
-  <si>
-    <t>E28</t>
-  </si>
-  <si>
     <t xml:space="preserve">PECLD </t>
   </si>
   <si>
@@ -120,6 +36,90 @@
   </si>
   <si>
     <t xml:space="preserve">Endividamento </t>
+  </si>
+  <si>
+    <t>Kepler Weber</t>
+  </si>
+  <si>
+    <t>Vulcabras</t>
+  </si>
+  <si>
+    <t>Unipar</t>
+  </si>
+  <si>
+    <t>Irani</t>
+  </si>
+  <si>
+    <t>Banrisul</t>
+  </si>
+  <si>
+    <t>Banco BMG</t>
+  </si>
+  <si>
+    <t>JHSF</t>
+  </si>
+  <si>
+    <t>BrasilAgro</t>
+  </si>
+  <si>
+    <t>Grendene</t>
+  </si>
+  <si>
+    <t>Desktop</t>
+  </si>
+  <si>
+    <t>Bemobi</t>
+  </si>
+  <si>
+    <t>Méliuz</t>
+  </si>
+  <si>
+    <t>Track &amp; Field</t>
+  </si>
+  <si>
+    <t>Boa Safra</t>
+  </si>
+  <si>
+    <t>Camil</t>
+  </si>
+  <si>
+    <t>Alliança Saúde</t>
+  </si>
+  <si>
+    <t>Pague Menos</t>
+  </si>
+  <si>
+    <t>Smart Fit</t>
+  </si>
+  <si>
+    <t>Plano &amp; Plano</t>
+  </si>
+  <si>
+    <t>OceanPact</t>
+  </si>
+  <si>
+    <t>Ecorodovias</t>
+  </si>
+  <si>
+    <t>Vivara</t>
+  </si>
+  <si>
+    <t>Copasa</t>
+  </si>
+  <si>
+    <t>Intelbras</t>
+  </si>
+  <si>
+    <t>Minerva Foods</t>
+  </si>
+  <si>
+    <t>Banco ABC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahle </t>
+  </si>
+  <si>
+    <t>Positivo</t>
   </si>
 </sst>
 </file>
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -173,9 +173,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,6 +457,7 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -468,18 +466,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <v>8.5</v>
@@ -492,8 +490,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="2">
         <v>9.1</v>
@@ -506,8 +504,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>7.9</v>
@@ -520,8 +518,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5" s="2">
         <v>10.199999999999999</v>
@@ -534,8 +532,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6" s="2">
         <v>8.8000000000000007</v>
@@ -548,8 +546,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
+      <c r="A7" t="s">
+        <v>29</v>
       </c>
       <c r="B7" s="2">
         <v>9.6999999999999993</v>
@@ -562,8 +560,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>8.1</v>
@@ -576,8 +574,8 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>10.5</v>
@@ -590,8 +588,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
+      <c r="A10" t="s">
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>7.6</v>
@@ -604,8 +602,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" t="s">
+        <v>11</v>
       </c>
       <c r="B11" s="2">
         <v>9.3000000000000007</v>
@@ -618,8 +616,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
+      <c r="A12" t="s">
+        <v>12</v>
       </c>
       <c r="B12" s="2">
         <v>1.2</v>
@@ -632,8 +630,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>12</v>
+      <c r="A13" t="s">
+        <v>31</v>
       </c>
       <c r="B13" s="2">
         <v>0.8</v>
@@ -646,7 +644,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="2">
@@ -660,7 +658,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="2">
@@ -674,7 +672,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="2">
@@ -688,7 +686,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17" s="2">
@@ -702,7 +700,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="2">
@@ -716,7 +714,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19" s="2">
@@ -730,7 +728,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="2">
@@ -744,7 +742,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="2">
@@ -758,7 +756,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="2">
@@ -772,7 +770,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
       <c r="B23" s="2">
@@ -786,7 +784,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="2">
@@ -800,7 +798,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="2">
@@ -814,7 +812,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
       <c r="B26" s="2">
@@ -828,8 +826,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>26</v>
+      <c r="A27" t="s">
+        <v>28</v>
       </c>
       <c r="B27" s="2">
         <v>5.3</v>
@@ -842,8 +840,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
+      <c r="A28" t="s">
+        <v>26</v>
       </c>
       <c r="B28" s="2">
         <v>4</v>
@@ -856,8 +854,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
+      <c r="A29" t="s">
+        <v>27</v>
       </c>
       <c r="B29" s="2">
         <v>5.7</v>
